--- a/docs/design/ACSMS-SCR-025/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_アカウントマスタ登録画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-025/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_アカウントマスタ登録画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1361,20 +1361,80 @@
       <c r="AG2" s="10" t="n"/>
       <c r="AH2" s="11" t="n"/>
     </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>実装との差分補完：カテゴリ8を新設し2件追加。069＝セキュリティ上重要な変更時のセッション全破棄（2026-07 のセキュリティレビュー対応）。パスワード変更/ロック(true)/ロール変更/所属変更では破棄し、ロック解除・氏名/メール/備考のみの変更・値が遷移しない更新では破棄しないこと、削除は無条件破棄、Redis 障害時も更新は成立し成功表示となることを確認する。070＝ログインIDの `SYSTEM` 予約名チェック（#55719）。`SYSTEM` 単体と `SYSTEM_` 始まりを大文字小文字問わず拒否し、`SYSTEMS`/`MYSYSTEM` は許可、DTO と DB の CHECK 制約の両方で防御することを確認する</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="19" t="inlineStr"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="19" t="inlineStr"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="AC2:AH2"/>
     <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="O3:V3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="W1:AB1"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="W3:AB3"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6314,7 +6374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ86"/>
+  <dimension ref="A1:BQ89"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -21629,8 +21689,871 @@
       <c r="BP86" s="10" t="n"/>
       <c r="BQ86" s="11" t="n"/>
     </row>
+    <row r="87" ht="22.5" customHeight="1">
+      <c r="A87" s="32" t="inlineStr">
+        <is>
+          <t>セッション破棄・予約名チェック（Session / Reserved-name）</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="n"/>
+      <c r="C87" s="10" t="n"/>
+      <c r="D87" s="10" t="n"/>
+      <c r="E87" s="10" t="n"/>
+      <c r="F87" s="10" t="n"/>
+      <c r="G87" s="10" t="n"/>
+      <c r="H87" s="10" t="n"/>
+      <c r="I87" s="10" t="n"/>
+      <c r="J87" s="10" t="n"/>
+      <c r="K87" s="10" t="n"/>
+      <c r="L87" s="10" t="n"/>
+      <c r="M87" s="10" t="n"/>
+      <c r="N87" s="10" t="n"/>
+      <c r="O87" s="10" t="n"/>
+      <c r="P87" s="10" t="n"/>
+      <c r="Q87" s="10" t="n"/>
+      <c r="R87" s="10" t="n"/>
+      <c r="S87" s="10" t="n"/>
+      <c r="T87" s="10" t="n"/>
+      <c r="U87" s="10" t="n"/>
+      <c r="V87" s="10" t="n"/>
+      <c r="W87" s="10" t="n"/>
+      <c r="X87" s="10" t="n"/>
+      <c r="Y87" s="10" t="n"/>
+      <c r="Z87" s="10" t="n"/>
+      <c r="AA87" s="10" t="n"/>
+      <c r="AB87" s="10" t="n"/>
+      <c r="AC87" s="10" t="n"/>
+      <c r="AD87" s="10" t="n"/>
+      <c r="AE87" s="10" t="n"/>
+      <c r="AF87" s="10" t="n"/>
+      <c r="AG87" s="10" t="n"/>
+      <c r="AH87" s="10" t="n"/>
+      <c r="AI87" s="10" t="n"/>
+      <c r="AJ87" s="10" t="n"/>
+      <c r="AK87" s="10" t="n"/>
+      <c r="AL87" s="10" t="n"/>
+      <c r="AM87" s="10" t="n"/>
+      <c r="AN87" s="10" t="n"/>
+      <c r="AO87" s="10" t="n"/>
+      <c r="AP87" s="10" t="n"/>
+      <c r="AQ87" s="10" t="n"/>
+      <c r="AR87" s="10" t="n"/>
+      <c r="AS87" s="10" t="n"/>
+      <c r="AT87" s="10" t="n"/>
+      <c r="AU87" s="10" t="n"/>
+      <c r="AV87" s="10" t="n"/>
+      <c r="AW87" s="10" t="n"/>
+      <c r="AX87" s="10" t="n"/>
+      <c r="AY87" s="10" t="n"/>
+      <c r="AZ87" s="10" t="n"/>
+      <c r="BA87" s="10" t="n"/>
+      <c r="BB87" s="10" t="n"/>
+      <c r="BC87" s="10" t="n"/>
+      <c r="BD87" s="10" t="n"/>
+      <c r="BE87" s="10" t="n"/>
+      <c r="BF87" s="10" t="n"/>
+      <c r="BG87" s="10" t="n"/>
+      <c r="BH87" s="10" t="n"/>
+      <c r="BI87" s="10" t="n"/>
+      <c r="BJ87" s="10" t="n"/>
+      <c r="BK87" s="10" t="n"/>
+      <c r="BL87" s="10" t="n"/>
+      <c r="BM87" s="10" t="n"/>
+      <c r="BN87" s="10" t="n"/>
+      <c r="BO87" s="10" t="n"/>
+      <c r="BP87" s="10" t="n"/>
+      <c r="BQ87" s="11" t="n"/>
+    </row>
+    <row r="88" ht="450" customHeight="1">
+      <c r="A88" s="44" t="n">
+        <v>69</v>
+      </c>
+      <c r="B88" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-025-069</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="n"/>
+      <c r="D88" s="11" t="n"/>
+      <c r="E88" s="46" t="inlineStr">
+        <is>
+          <t>セキュリティ上重要な変更時のセッション破棄（de-provisioning）</t>
+        </is>
+      </c>
+      <c r="F88" s="10" t="n"/>
+      <c r="G88" s="10" t="n"/>
+      <c r="H88" s="10" t="n"/>
+      <c r="I88" s="11" t="n"/>
+      <c r="J88" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN（`account.update` / `account.delete` 権限あり）
+・対象アカウント B（JA_HONTEN）が**別ブラウザでログイン済み**であること（有効な session cookie を保持）
+・Redis を一時的に停止できる環境も用意すること（ステップ8用）</t>
+        </is>
+      </c>
+      <c r="K88" s="10" t="n"/>
+      <c r="L88" s="10" t="n"/>
+      <c r="M88" s="10" t="n"/>
+      <c r="N88" s="10" t="n"/>
+      <c r="O88" s="10" t="n"/>
+      <c r="P88" s="11" t="n"/>
+      <c r="Q88" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">管理者が B のパスワードを強制リセットする。その後、B のブラウザで任意の画面を操作する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">B を再ログインさせたうえで、管理者が B の管理者区分（ロール）を変更する。その後 B のブラウザで操作する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">B を再ログインさせたうえで、管理者が B の所属（JA・管理支店・所属支店のいずれか）を変更する。その後 B のブラウザで操作する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">B を再ログインさせたうえで、管理者が B を**ロック**する。その後 B のブラウザで操作する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">B を再ログインさせたうえで、管理者が B の**ロックを解除**する。その後 B のブラウザで操作する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">B を再ログインさせたうえで、管理者が B の**氏名・メールアドレス・備考のみ**を変更する。その後 B のブラウザで操作する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ7：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">B を再ログインさせたうえで、管理者が B を**削除**する。その後 B のブラウザで操作する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ8：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Redis を停止した状態で管理者が B のロールを変更する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ9：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>所属を「変更していない」更新（同じ値を再送信）を行う</t>
+          </r>
+        </is>
+      </c>
+      <c r="R88" s="10" t="n"/>
+      <c r="S88" s="10" t="n"/>
+      <c r="T88" s="10" t="n"/>
+      <c r="U88" s="10" t="n"/>
+      <c r="V88" s="10" t="n"/>
+      <c r="W88" s="11" t="n"/>
+      <c r="X88" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">B のセッションが破棄され、401 → ログイン画面へ遷移すること（再ログインが必須）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">同様にセッションが破棄されること。**旧ロールの権限が残らない**こと（セッションのペイロードはログイン時に固定されるため、破棄しないと降格が反映されない）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">同様にセッションが破棄されること（`ja_id` / `kanri_shiten_id` / `shiten_id` もログイン時固定のため）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">セッションが破棄され、B は以後ログインもできないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">**セッションは破棄されないこと**。ロック解除の操作で管理者自身のセッションを切ってはならないため
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">**セッションは破棄されないこと**（非機密の変更）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ7：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">セッションが破棄されること（削除は無条件に破棄する）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ8：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">更新自体は成功し画面に成功メッセージが表示されること。サーバーログに破棄失敗の警告が出力されること（破棄はコミット後のベストエフォート。業務書き込みは成立済みで、セッションは24時間のTTL内に失効する）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ9：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">セッションが破棄されないこと（`undefined`＝更新に含まれない と `null`＝スコープなし を正規化し、**実際に値が遷移した場合のみ**変更とみなす）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・2026-07 のセキュリティレビュー対応。`SessionAuthGuard` は Redis のセッションを引くだけで DB を再検証しないため、破棄しないと退職者・無効化アカウントが cookie のまま元の権限を保持し続ける（de-provisioning bypass）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・ステップ5・6・9 は「破棄しすぎない」ことの確認。過剰に破棄すると管理者が自分のセッションを切る／利用者が些細な変更のたびに追い出される</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y88" s="10" t="n"/>
+      <c r="Z88" s="10" t="n"/>
+      <c r="AA88" s="10" t="n"/>
+      <c r="AB88" s="10" t="n"/>
+      <c r="AC88" s="10" t="n"/>
+      <c r="AD88" s="11" t="n"/>
+      <c r="AE88" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF88" s="11" t="n"/>
+      <c r="AG88" s="45" t="inlineStr"/>
+      <c r="AH88" s="10" t="n"/>
+      <c r="AI88" s="11" t="n"/>
+      <c r="AJ88" s="45" t="inlineStr"/>
+      <c r="AK88" s="10" t="n"/>
+      <c r="AL88" s="11" t="n"/>
+      <c r="AM88" s="45" t="inlineStr"/>
+      <c r="AN88" s="10" t="n"/>
+      <c r="AO88" s="11" t="n"/>
+      <c r="AP88" s="45" t="inlineStr"/>
+      <c r="AQ88" s="10" t="n"/>
+      <c r="AR88" s="11" t="n"/>
+      <c r="AS88" s="45" t="inlineStr"/>
+      <c r="AT88" s="10" t="n"/>
+      <c r="AU88" s="11" t="n"/>
+      <c r="AV88" s="45" t="inlineStr"/>
+      <c r="AW88" s="10" t="n"/>
+      <c r="AX88" s="11" t="n"/>
+      <c r="AY88" s="45" t="inlineStr"/>
+      <c r="AZ88" s="10" t="n"/>
+      <c r="BA88" s="11" t="n"/>
+      <c r="BB88" s="45" t="inlineStr"/>
+      <c r="BC88" s="10" t="n"/>
+      <c r="BD88" s="11" t="n"/>
+      <c r="BE88" s="45" t="inlineStr"/>
+      <c r="BF88" s="10" t="n"/>
+      <c r="BG88" s="11" t="n"/>
+      <c r="BH88" s="45" t="inlineStr"/>
+      <c r="BI88" s="10" t="n"/>
+      <c r="BJ88" s="11" t="n"/>
+      <c r="BK88" s="46" t="inlineStr"/>
+      <c r="BL88" s="10" t="n"/>
+      <c r="BM88" s="10" t="n"/>
+      <c r="BN88" s="10" t="n"/>
+      <c r="BO88" s="10" t="n"/>
+      <c r="BP88" s="10" t="n"/>
+      <c r="BQ88" s="11" t="n"/>
+    </row>
+    <row r="89" ht="450" customHeight="1">
+      <c r="A89" s="44" t="n">
+        <v>70</v>
+      </c>
+      <c r="B89" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-025-070</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="n"/>
+      <c r="D89" s="11" t="n"/>
+      <c r="E89" s="46" t="inlineStr">
+        <is>
+          <t>ログインIDの SYSTEM 予約名チェック（#55719）</t>
+        </is>
+      </c>
+      <c r="F89" s="10" t="n"/>
+      <c r="G89" s="10" t="n"/>
+      <c r="H89" s="10" t="n"/>
+      <c r="I89" s="11" t="n"/>
+      <c r="J89" s="46" t="inlineStr">
+        <is>
+          <t>・role: NICHINO_ADMIN（`account.create` 権限あり）
+・アカウント登録画面（新規モード）を開いていること</t>
+        </is>
+      </c>
+      <c r="K89" s="10" t="n"/>
+      <c r="L89" s="10" t="n"/>
+      <c r="M89" s="10" t="n"/>
+      <c r="N89" s="10" t="n"/>
+      <c r="O89" s="10" t="n"/>
+      <c r="P89" s="11" t="n"/>
+      <c r="Q89" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ログインIDに `SYSTEM` を入力して登録する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ログインIDに `system`（小文字）を入力して登録する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ログインIDに `SYSTEM_DENSHI_SYNC` を入力して登録する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ログインIDに `System_batch` を入力して登録する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ログインIDに `SYSTEMS`（`SYSTEM` で始まるが `SYSTEM_` ではない）を入力して登録する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ログインIDに `MYSYSTEM`（末尾が SYSTEM）を入力して登録する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ7：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>DevTools から DTO を迂回して直接 INSERT 相当のリクエストを送る（DB の CHECK 制約の確認）</t>
+          </r>
+        </is>
+      </c>
+      <c r="R89" s="10" t="n"/>
+      <c r="S89" s="10" t="n"/>
+      <c r="T89" s="10" t="n"/>
+      <c r="U89" s="10" t="n"/>
+      <c r="V89" s="10" t="n"/>
+      <c r="W89" s="11" t="n"/>
+      <c r="X89" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">入力エラーとなり登録できないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">入力エラーとなること（**大文字小文字を区別しない**）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">入力エラーとなること（`SYSTEM_` で始まる文字列は予約済み）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">入力エラーとなること（大文字小文字を区別せず `SYSTEM_` 始まりと判定）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">登録できること（`SYSTEM` 単体でも `SYSTEM_` 始まりでもない）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">登録できること（前方一致のみを禁止する）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ7：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">DB の CHECK 制約 `ck_m_account_login_id_not_reserved` により拒否されること（DTO と DB の**両方**で防御する）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・バッチの実行者名（`SYSTEM_DENSHI_SYNC` 等）と衝突すると、`t_dokusya_rireki.created_by` による「電子版同期由来か画面操作由来か」の判別が壊れるため（#55719）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・SCR-013 の履歴一覧では `created_by` が `SYSTEM_*` かどうかで表示を分けている（ACSMS-TC-013-040 参照）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y89" s="10" t="n"/>
+      <c r="Z89" s="10" t="n"/>
+      <c r="AA89" s="10" t="n"/>
+      <c r="AB89" s="10" t="n"/>
+      <c r="AC89" s="10" t="n"/>
+      <c r="AD89" s="11" t="n"/>
+      <c r="AE89" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF89" s="11" t="n"/>
+      <c r="AG89" s="45" t="inlineStr"/>
+      <c r="AH89" s="10" t="n"/>
+      <c r="AI89" s="11" t="n"/>
+      <c r="AJ89" s="45" t="inlineStr"/>
+      <c r="AK89" s="10" t="n"/>
+      <c r="AL89" s="11" t="n"/>
+      <c r="AM89" s="45" t="inlineStr"/>
+      <c r="AN89" s="10" t="n"/>
+      <c r="AO89" s="11" t="n"/>
+      <c r="AP89" s="45" t="inlineStr"/>
+      <c r="AQ89" s="10" t="n"/>
+      <c r="AR89" s="11" t="n"/>
+      <c r="AS89" s="45" t="inlineStr"/>
+      <c r="AT89" s="10" t="n"/>
+      <c r="AU89" s="11" t="n"/>
+      <c r="AV89" s="45" t="inlineStr"/>
+      <c r="AW89" s="10" t="n"/>
+      <c r="AX89" s="11" t="n"/>
+      <c r="AY89" s="45" t="inlineStr"/>
+      <c r="AZ89" s="10" t="n"/>
+      <c r="BA89" s="11" t="n"/>
+      <c r="BB89" s="45" t="inlineStr"/>
+      <c r="BC89" s="10" t="n"/>
+      <c r="BD89" s="11" t="n"/>
+      <c r="BE89" s="45" t="inlineStr"/>
+      <c r="BF89" s="10" t="n"/>
+      <c r="BG89" s="11" t="n"/>
+      <c r="BH89" s="45" t="inlineStr"/>
+      <c r="BI89" s="10" t="n"/>
+      <c r="BJ89" s="11" t="n"/>
+      <c r="BK89" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL89" s="10" t="n"/>
+      <c r="BM89" s="10" t="n"/>
+      <c r="BN89" s="10" t="n"/>
+      <c r="BO89" s="10" t="n"/>
+      <c r="BP89" s="10" t="n"/>
+      <c r="BQ89" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="1229">
+  <mergeCells count="1264">
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="Q27:W27"/>
     <mergeCell ref="BH33:BJ33"/>
@@ -21654,6 +22577,7 @@
     <mergeCell ref="AS51:AU51"/>
     <mergeCell ref="J75:P75"/>
     <mergeCell ref="AV81:AX81"/>
+    <mergeCell ref="BB88:BD88"/>
     <mergeCell ref="AE31:AF31"/>
     <mergeCell ref="H7:J7"/>
     <mergeCell ref="AS67:AU67"/>
@@ -21732,6 +22656,7 @@
     <mergeCell ref="AG11:AI11"/>
     <mergeCell ref="BH53:BJ53"/>
     <mergeCell ref="AP63:AR63"/>
+    <mergeCell ref="BK88:BQ88"/>
     <mergeCell ref="BH48:BJ48"/>
     <mergeCell ref="T8:V8"/>
     <mergeCell ref="BE39:BG39"/>
@@ -21807,6 +22732,7 @@
     <mergeCell ref="BE76:BG76"/>
     <mergeCell ref="AG76:AI76"/>
     <mergeCell ref="X60:AD60"/>
+    <mergeCell ref="B88:D88"/>
     <mergeCell ref="B82:D82"/>
     <mergeCell ref="BB41:BD41"/>
     <mergeCell ref="J46:P46"/>
@@ -21817,8 +22743,10 @@
     <mergeCell ref="AS13:AU13"/>
     <mergeCell ref="B85:D85"/>
     <mergeCell ref="AS15:AU15"/>
+    <mergeCell ref="BE89:BG89"/>
     <mergeCell ref="BK52:BQ52"/>
     <mergeCell ref="X73:AD73"/>
+    <mergeCell ref="BE88:BG88"/>
     <mergeCell ref="H6:J6"/>
     <mergeCell ref="AS25:AU25"/>
     <mergeCell ref="B14:D14"/>
@@ -21838,6 +22766,7 @@
     <mergeCell ref="AS81:AU81"/>
     <mergeCell ref="AV82:AX82"/>
     <mergeCell ref="BE47:BG47"/>
+    <mergeCell ref="AM88:AO88"/>
     <mergeCell ref="AM82:AO82"/>
     <mergeCell ref="AM54:AO54"/>
     <mergeCell ref="BE40:BG40"/>
@@ -21869,6 +22798,7 @@
     <mergeCell ref="X43:AD43"/>
     <mergeCell ref="BK15:BQ15"/>
     <mergeCell ref="AE17:AF17"/>
+    <mergeCell ref="J88:P88"/>
     <mergeCell ref="E15:I15"/>
     <mergeCell ref="AS24:AU24"/>
     <mergeCell ref="AE19:AF19"/>
@@ -21894,6 +22824,7 @@
     <mergeCell ref="J15:P15"/>
     <mergeCell ref="AJ11:AL11"/>
     <mergeCell ref="E54:I54"/>
+    <mergeCell ref="AS88:AU88"/>
     <mergeCell ref="AS63:AU63"/>
     <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="E56:I56"/>
@@ -21928,6 +22859,8 @@
     <mergeCell ref="BK32:BQ32"/>
     <mergeCell ref="AE28:AF28"/>
     <mergeCell ref="AY86:BA86"/>
+    <mergeCell ref="Q88:W88"/>
+    <mergeCell ref="BB89:BD89"/>
     <mergeCell ref="X80:AD80"/>
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="BB82:BD82"/>
@@ -21986,7 +22919,9 @@
     <mergeCell ref="AV25:AX25"/>
     <mergeCell ref="W6:Y6"/>
     <mergeCell ref="BK68:BQ68"/>
+    <mergeCell ref="X89:AD89"/>
     <mergeCell ref="BK67:BQ67"/>
+    <mergeCell ref="X88:AD88"/>
     <mergeCell ref="AE63:AF63"/>
     <mergeCell ref="AC8:AE8"/>
     <mergeCell ref="AP69:AR69"/>
@@ -22007,6 +22942,7 @@
     <mergeCell ref="BH47:BJ47"/>
     <mergeCell ref="X20:AD20"/>
     <mergeCell ref="BH74:BJ74"/>
+    <mergeCell ref="AP88:AR88"/>
     <mergeCell ref="X14:AD14"/>
     <mergeCell ref="AP82:AR82"/>
     <mergeCell ref="B42:D42"/>
@@ -22028,6 +22964,7 @@
     <mergeCell ref="J36:P36"/>
     <mergeCell ref="AY66:BA66"/>
     <mergeCell ref="AV21:AX21"/>
+    <mergeCell ref="BH89:BJ89"/>
     <mergeCell ref="AV29:AX29"/>
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="AY68:BA68"/>
@@ -22130,6 +23067,7 @@
     <mergeCell ref="AG36:AI36"/>
     <mergeCell ref="B78:D78"/>
     <mergeCell ref="BB31:BD31"/>
+    <mergeCell ref="E88:I88"/>
     <mergeCell ref="Q32:W32"/>
     <mergeCell ref="E82:I82"/>
     <mergeCell ref="X22:AD22"/>
@@ -22168,9 +23106,11 @@
     <mergeCell ref="AJ77:AL77"/>
     <mergeCell ref="BK84:BQ84"/>
     <mergeCell ref="BK86:BQ86"/>
+    <mergeCell ref="AE88:AF88"/>
     <mergeCell ref="AE82:AF82"/>
     <mergeCell ref="BH36:BJ36"/>
     <mergeCell ref="BH11:BJ11"/>
+    <mergeCell ref="AS89:AU89"/>
     <mergeCell ref="AJ59:AL59"/>
     <mergeCell ref="AG25:AI25"/>
     <mergeCell ref="AE83:AF83"/>
@@ -22252,6 +23192,7 @@
     <mergeCell ref="B80:D80"/>
     <mergeCell ref="A26:BQ26"/>
     <mergeCell ref="AY74:BA74"/>
+    <mergeCell ref="AG88:AI88"/>
     <mergeCell ref="AG82:AI82"/>
     <mergeCell ref="AY76:BA76"/>
     <mergeCell ref="BK47:BQ47"/>
@@ -22267,6 +23208,7 @@
     <mergeCell ref="E20:I20"/>
     <mergeCell ref="BK37:BQ37"/>
     <mergeCell ref="AP66:AR66"/>
+    <mergeCell ref="AY89:BA89"/>
     <mergeCell ref="BK66:BQ66"/>
     <mergeCell ref="BH60:BJ60"/>
     <mergeCell ref="AC7:AE7"/>
@@ -22307,6 +23249,7 @@
     <mergeCell ref="AM63:AO63"/>
     <mergeCell ref="BB46:BD46"/>
     <mergeCell ref="BE57:BG57"/>
+    <mergeCell ref="B89:D89"/>
     <mergeCell ref="BB48:BD48"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="Q51:W51"/>
@@ -22330,8 +23273,10 @@
     <mergeCell ref="E44:I44"/>
     <mergeCell ref="BE58:BG58"/>
     <mergeCell ref="AJ65:AL65"/>
+    <mergeCell ref="AV89:AX89"/>
     <mergeCell ref="J29:P29"/>
     <mergeCell ref="BB17:BD17"/>
+    <mergeCell ref="AM89:AO89"/>
     <mergeCell ref="BB11:BD11"/>
     <mergeCell ref="AJ25:AL25"/>
     <mergeCell ref="BE53:BG53"/>
@@ -22419,6 +23364,7 @@
     <mergeCell ref="BB81:BD81"/>
     <mergeCell ref="AY11:BA11"/>
     <mergeCell ref="Q57:W57"/>
+    <mergeCell ref="AJ88:AL88"/>
     <mergeCell ref="AP17:AR17"/>
     <mergeCell ref="AY40:BA40"/>
     <mergeCell ref="Q42:W42"/>
@@ -22530,8 +23476,10 @@
     <mergeCell ref="AM68:AO68"/>
     <mergeCell ref="BH52:BJ52"/>
     <mergeCell ref="BH81:BJ81"/>
+    <mergeCell ref="AP89:AR89"/>
     <mergeCell ref="BE11:BG11"/>
     <mergeCell ref="B49:D49"/>
+    <mergeCell ref="BK89:BQ89"/>
     <mergeCell ref="B65:D65"/>
     <mergeCell ref="T7:V7"/>
     <mergeCell ref="X52:AD52"/>
@@ -22569,6 +23517,7 @@
     <mergeCell ref="E14:I14"/>
     <mergeCell ref="AM64:AO64"/>
     <mergeCell ref="AS48:AU48"/>
+    <mergeCell ref="A87:BQ87"/>
     <mergeCell ref="AE43:AF43"/>
     <mergeCell ref="AV86:AX86"/>
     <mergeCell ref="BE13:BG13"/>
@@ -22654,6 +23603,7 @@
     <mergeCell ref="BH58:BJ58"/>
     <mergeCell ref="BB36:BD36"/>
     <mergeCell ref="Q39:W39"/>
+    <mergeCell ref="E89:I89"/>
     <mergeCell ref="AJ75:AL75"/>
     <mergeCell ref="J74:P74"/>
     <mergeCell ref="J49:P49"/>
@@ -22676,7 +23626,9 @@
     <mergeCell ref="X48:AD48"/>
     <mergeCell ref="AE23:AF23"/>
     <mergeCell ref="Q83:W83"/>
+    <mergeCell ref="AG89:AI89"/>
     <mergeCell ref="BB75:BD75"/>
+    <mergeCell ref="J89:P89"/>
     <mergeCell ref="Q85:W85"/>
     <mergeCell ref="AS54:AU54"/>
     <mergeCell ref="Q78:W78"/>
@@ -22701,6 +23653,7 @@
     <mergeCell ref="BH16:BJ16"/>
     <mergeCell ref="AM29:AO29"/>
     <mergeCell ref="AM23:AO23"/>
+    <mergeCell ref="AE89:AF89"/>
     <mergeCell ref="AG72:AI72"/>
     <mergeCell ref="BB58:BD58"/>
     <mergeCell ref="J47:P47"/>
@@ -22727,9 +23680,11 @@
     <mergeCell ref="BK34:BQ34"/>
     <mergeCell ref="AY59:BA59"/>
     <mergeCell ref="BH82:BJ82"/>
+    <mergeCell ref="BH88:BJ88"/>
     <mergeCell ref="J58:P58"/>
     <mergeCell ref="AP11:AR11"/>
     <mergeCell ref="BK36:BQ36"/>
+    <mergeCell ref="AY88:BA88"/>
     <mergeCell ref="AS47:AU47"/>
     <mergeCell ref="AY54:BA54"/>
     <mergeCell ref="BH83:BJ83"/>
@@ -22743,6 +23698,7 @@
     <mergeCell ref="X83:AD83"/>
     <mergeCell ref="AP64:AR64"/>
     <mergeCell ref="BK64:BQ64"/>
+    <mergeCell ref="Q89:W89"/>
     <mergeCell ref="X85:AD85"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="AE59:AF59"/>
@@ -22794,6 +23750,7 @@
     <mergeCell ref="E22:I22"/>
     <mergeCell ref="BK73:BQ73"/>
     <mergeCell ref="BH31:BJ31"/>
+    <mergeCell ref="AV88:AX88"/>
     <mergeCell ref="AP74:AR74"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B28:D28"/>
@@ -22835,6 +23792,7 @@
     <mergeCell ref="X63:AD63"/>
     <mergeCell ref="AE20:AF20"/>
     <mergeCell ref="AS27:AU27"/>
+    <mergeCell ref="AJ89:AL89"/>
     <mergeCell ref="AE38:AF38"/>
     <mergeCell ref="AV54:AX54"/>
     <mergeCell ref="AS45:AU45"/>
@@ -22862,13 +23820,13 @@
     <mergeCell ref="BE60:BG60"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE17 AE19:AE25 AE27:AE29 AE31:AE60 AE62:AE69 AE71:AE78 AE80:AE86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE17 AE19:AE25 AE27:AE29 AE31:AE60 AE62:AE69 AE71:AE78 AE80:AE86 AE88:AE89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG17 AG19:AG25 AG27:AG29 AG31:AG60 AG62:AG69 AG71:AG78 AG80:AG86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG17 AG19:AG25 AG27:AG29 AG31:AG60 AG62:AG69 AG71:AG78 AG80:AG86 AG88:AG89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV17 AV19:AV25 AV27:AV29 AV31:AV60 AV62:AV69 AV71:AV78 AV80:AV86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV17 AV19:AV25 AV27:AV29 AV31:AV60 AV62:AV69 AV71:AV78 AV80:AV86 AV88:AV89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
